--- a/Assets/Game/Content/Data/TipTable.xlsx
+++ b/Assets/Game/Content/Data/TipTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlier\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C13CFA-47EF-4428-8525-7BE12CF5768B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A2AE30-59FF-46A7-B32D-947BE7C0C9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="156">
   <si>
     <t>Id</t>
   </si>
@@ -166,12 +166,6 @@
     <t>Player_Essence</t>
   </si>
   <si>
-    <t>Tip_Player_Essence</t>
-  </si>
-  <si>
-    <t>Tip_Player_Essence_Desc</t>
-  </si>
-  <si>
     <t>Shop_Refresh</t>
   </si>
   <si>
@@ -416,11 +410,11 @@
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -436,7 +430,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -462,7 +456,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -478,7 +472,7 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -504,7 +498,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ChooseLevel_Boss</t>
@@ -514,87 +508,114 @@
   </si>
   <si>
     <t>ChooseLevel_Sample</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card_Sturdy</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card_Reflect</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Recycle</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Recycle_Desc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card_Focus</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card_Tailwind</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card_Windborne</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player_Use</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Essence_Desc</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Essence</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Use</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Use_Desc</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -666,10 +687,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -948,12 +970,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.09765625" customWidth="1"/>
     <col min="2" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,39 +1178,39 @@
       <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
+      <c r="B18" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
@@ -1196,13 +1218,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
@@ -1210,13 +1232,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
@@ -1224,55 +1246,55 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
         <v>58</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>59</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B27" t="s">
         <v>60</v>
       </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C27" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="D27" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
@@ -1280,41 +1302,41 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
         <v>70</v>
       </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="D31" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>130</v>
+      <c r="B33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
@@ -1322,20 +1344,34 @@
     </row>
     <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>132</v>
       </c>
-      <c r="D34" t="s">
+      <c r="B35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1343,10 +1379,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.09765625" customWidth="1"/>
+    <col min="2" max="2" width="22.19921875" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
   </cols>
@@ -1367,328 +1403,328 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
         <v>73</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
         <v>77</v>
       </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
         <v>80</v>
       </c>
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
         <v>84</v>
       </c>
-      <c r="B6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
         <v>87</v>
       </c>
-      <c r="B7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>89</v>
-      </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
         <v>90</v>
       </c>
-      <c r="B8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
         <v>93</v>
       </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
         <v>96</v>
       </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
         <v>99</v>
       </c>
-      <c r="B11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" t="s">
         <v>102</v>
       </c>
-      <c r="B12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" t="s">
         <v>105</v>
       </c>
-      <c r="B13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" t="s">
-        <v>107</v>
-      </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
         <v>108</v>
       </c>
-      <c r="B14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s">
         <v>111</v>
       </c>
-      <c r="B15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>146</v>
-      </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
         <v>115</v>
       </c>
-      <c r="B23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" t="s">
-        <v>117</v>
-      </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
         <v>118</v>
       </c>
-      <c r="B24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" t="s">
-        <v>120</v>
-      </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s">
         <v>121</v>
       </c>
-      <c r="B25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" t="s">
-        <v>123</v>
-      </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
         <v>124</v>
       </c>
-      <c r="B26" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" t="s">
-        <v>126</v>
-      </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Game/Content/Data/TipTable.xlsx
+++ b/Assets/Game/Content/Data/TipTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A2AE30-59FF-46A7-B32D-947BE7C0C9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA422FCF-7C2C-4C6C-95C7-410D63A2C3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="159">
   <si>
     <t>Id</t>
   </si>
@@ -410,11 +410,11 @@
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -430,7 +430,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -456,7 +456,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -472,7 +472,7 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -498,7 +498,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ChooseLevel_Boss</t>
@@ -508,107 +508,126 @@
   </si>
   <si>
     <t>ChooseLevel_Sample</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Card_Sturdy</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Card_Reflect</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Recycle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Recycle_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Card_Focus</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Card_Tailwind</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Card_Windborne</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Player_Use</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Essence_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Essence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use_Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_Aftermath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Aftermath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Aftermath_Desc</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -687,17 +706,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -971,14 +991,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.09765625" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
     <col min="2" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="15.796875" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -992,7 +1012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1006,7 +1026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1020,7 +1040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1034,7 +1054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1048,7 +1068,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1062,7 +1082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1076,7 +1096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1090,7 +1110,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1104,7 +1124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1118,7 +1138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1132,7 +1152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1146,7 +1166,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -1160,7 +1180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1174,7 +1194,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1188,7 +1208,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
         <v>151</v>
       </c>
@@ -1202,7 +1222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1216,7 +1236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -1230,7 +1250,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1244,7 +1264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1258,7 +1278,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -1272,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -1286,7 +1306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1300,7 +1320,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>65</v>
       </c>
@@ -1314,7 +1334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -1328,7 +1348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="15.6">
       <c r="A33" s="3" t="s">
         <v>133</v>
       </c>
@@ -1342,7 +1362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="15.6">
       <c r="A34" t="s">
         <v>131</v>
       </c>
@@ -1356,7 +1376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="15.6">
       <c r="A35" t="s">
         <v>132</v>
       </c>
@@ -1371,23 +1391,23 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16.09765625" customWidth="1"/>
-    <col min="2" max="2" width="22.19921875" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1401,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -1415,7 +1435,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -1429,7 +1449,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -1443,7 +1463,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1457,7 +1477,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -1471,7 +1491,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -1485,7 +1505,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>91</v>
       </c>
@@ -1499,7 +1519,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -1513,7 +1533,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>97</v>
       </c>
@@ -1527,7 +1547,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -1541,7 +1561,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>103</v>
       </c>
@@ -1555,7 +1575,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -1569,7 +1589,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>109</v>
       </c>
@@ -1583,7 +1603,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>112</v>
       </c>
@@ -1597,7 +1617,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
         <v>134</v>
       </c>
@@ -1611,7 +1631,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
         <v>135</v>
       </c>
@@ -1625,7 +1645,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
         <v>142</v>
       </c>
@@ -1639,7 +1659,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
         <v>145</v>
       </c>
@@ -1653,7 +1673,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21" s="5" t="s">
         <v>150</v>
       </c>
@@ -1667,64 +1687,78 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
         <v>113</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B28" t="s">
         <v>114</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C28" t="s">
         <v>115</v>
       </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="D28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B29" t="s">
         <v>117</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C29" t="s">
         <v>118</v>
       </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="D29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
         <v>119</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B30" t="s">
         <v>120</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C30" t="s">
         <v>121</v>
       </c>
-      <c r="D25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="D30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>122</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B31" t="s">
         <v>123</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C31" t="s">
         <v>124</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D31" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Game/Content/Data/TipTable.xlsx
+++ b/Assets/Game/Content/Data/TipTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA422FCF-7C2C-4C6C-95C7-410D63A2C3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10966519-D4B7-4AB0-A09B-945FAB4C3A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
